--- a/csv/model/fuels/formula_fuels_CIMS.xlsx
+++ b/csv/model/fuels/formula_fuels_CIMS.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="31935" yWindow="1335" windowWidth="17280" windowHeight="8475" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3624" yWindow="2148" windowWidth="17280" windowHeight="8880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -12,7 +12,7 @@
     <externalReference r:id="rId2"/>
   </externalReferences>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1" iterate="1" calcCompleted="0" calcOnSave="0"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" calcOnSave="0"/>
 </workbook>
 </file>
 
@@ -27216,7 +27216,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -27353,7 +27353,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Service provided</t>
+          <t>service_provide</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -27385,7 +27385,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Competition type</t>
+          <t>competition</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -27417,7 +27417,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Service provided</t>
+          <t>service_provide</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -27449,7 +27449,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Competition type</t>
+          <t>competition</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -27481,7 +27481,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Is supply</t>
+          <t>is_supply</t>
         </is>
       </c>
       <c r="H7" t="b">
@@ -27511,7 +27511,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>LCC_financial</t>
+          <t>lcc_financial</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -27597,7 +27597,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Emissions_biomass</t>
+          <t>emissions_biomass</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -27688,7 +27688,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -27779,7 +27779,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -27870,7 +27870,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -27961,7 +27961,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Service provided</t>
+          <t>service_provide</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -27993,7 +27993,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Competition type</t>
+          <t>competition</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -28025,7 +28025,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Is supply</t>
+          <t>is_supply</t>
         </is>
       </c>
       <c r="H15" t="b">
@@ -28055,7 +28055,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>LCC_financial</t>
+          <t>lcc_financial</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -28130,7 +28130,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Emissions_biomass</t>
+          <t>emissions_biomass</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -28221,7 +28221,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -28312,7 +28312,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -28403,7 +28403,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -28494,7 +28494,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Service provided</t>
+          <t>service_provide</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -28526,7 +28526,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Competition type</t>
+          <t>competition</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -28558,7 +28558,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Is supply</t>
+          <t>is_supply</t>
         </is>
       </c>
       <c r="H23" t="b">
@@ -28588,7 +28588,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>LCC_financial</t>
+          <t>lcc_financial</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -28674,7 +28674,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -28765,7 +28765,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -28856,7 +28856,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -28947,7 +28947,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Service provided</t>
+          <t>service_provide</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -28979,7 +28979,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Competition type</t>
+          <t>competition</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -29011,7 +29011,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Is supply</t>
+          <t>is_supply</t>
         </is>
       </c>
       <c r="H30" t="b">
@@ -29041,7 +29041,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>LCC_financial</t>
+          <t>lcc_financial</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -29127,7 +29127,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -29218,7 +29218,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -29309,7 +29309,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -29400,7 +29400,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -29491,7 +29491,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Service provided</t>
+          <t>service_provide</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -29523,7 +29523,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Competition type</t>
+          <t>competition</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -29555,7 +29555,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Is supply</t>
+          <t>is_supply</t>
         </is>
       </c>
       <c r="H38" t="b">
@@ -29585,7 +29585,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>LCC_financial</t>
+          <t>lcc_financial</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -29671,7 +29671,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -29762,7 +29762,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -29853,7 +29853,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -29944,7 +29944,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Service provided</t>
+          <t>service_provide</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -29976,7 +29976,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Competition type</t>
+          <t>competition</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -30008,7 +30008,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Is supply</t>
+          <t>is_supply</t>
         </is>
       </c>
       <c r="H45" t="b">
@@ -30038,7 +30038,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>LCC_financial</t>
+          <t>lcc_financial</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -30124,7 +30124,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -30215,7 +30215,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -30306,7 +30306,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -30397,7 +30397,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Service provided</t>
+          <t>service_provide</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -30429,7 +30429,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Competition type</t>
+          <t>competition</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -30461,7 +30461,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Is supply</t>
+          <t>is_supply</t>
         </is>
       </c>
       <c r="H52" t="b">
@@ -30491,7 +30491,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>LCC_financial</t>
+          <t>lcc_financial</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -30577,7 +30577,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -30668,7 +30668,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -30759,7 +30759,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -30850,7 +30850,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Service provided</t>
+          <t>service_provide</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -30882,7 +30882,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Competition type</t>
+          <t>competition</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -30914,7 +30914,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Is supply</t>
+          <t>is_supply</t>
         </is>
       </c>
       <c r="H59" t="b">
@@ -30944,7 +30944,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>LCC_financial</t>
+          <t>lcc_financial</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -31030,7 +31030,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -31121,7 +31121,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -31212,7 +31212,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -31303,7 +31303,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Service provided</t>
+          <t>service_provide</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -31335,7 +31335,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Competition type</t>
+          <t>competition</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -31367,7 +31367,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Is supply</t>
+          <t>is_supply</t>
         </is>
       </c>
       <c r="H66" t="b">
@@ -31397,7 +31397,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>LCC_financial</t>
+          <t>lcc_financial</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -31483,7 +31483,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -31574,7 +31574,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -31665,7 +31665,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -31756,7 +31756,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Service provided</t>
+          <t>service_provide</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -31788,7 +31788,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Competition type</t>
+          <t>competition</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -31820,7 +31820,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Is supply</t>
+          <t>is_supply</t>
         </is>
       </c>
       <c r="H73" t="b">
@@ -31850,7 +31850,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>LCC_financial</t>
+          <t>lcc_financial</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -31936,7 +31936,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -32027,7 +32027,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -32118,7 +32118,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -32209,7 +32209,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Service provided</t>
+          <t>service_provide</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -32241,7 +32241,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Competition type</t>
+          <t>competition</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -32273,7 +32273,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Is supply</t>
+          <t>is_supply</t>
         </is>
       </c>
       <c r="H80" t="b">
@@ -32303,7 +32303,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>LCC_financial</t>
+          <t>lcc_financial</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -32389,7 +32389,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -32480,7 +32480,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -32571,7 +32571,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -32662,7 +32662,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Service provided</t>
+          <t>service_provide</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -32694,7 +32694,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Competition type</t>
+          <t>competition</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -32726,7 +32726,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Is supply</t>
+          <t>is_supply</t>
         </is>
       </c>
       <c r="H87" t="b">
@@ -32756,7 +32756,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>LCC_financial</t>
+          <t>lcc_financial</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -32837,7 +32837,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Service provided</t>
+          <t>service_provide</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -32869,7 +32869,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Competition type</t>
+          <t>competition</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -32901,7 +32901,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Is supply</t>
+          <t>is_supply</t>
         </is>
       </c>
       <c r="H91" t="b">
@@ -32931,7 +32931,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>LCC_financial</t>
+          <t>lcc_financial</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -33017,7 +33017,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -33108,7 +33108,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -33199,7 +33199,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -33290,7 +33290,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Service provided</t>
+          <t>service_provide</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -33322,7 +33322,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Competition type</t>
+          <t>competition</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -33354,7 +33354,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Is supply</t>
+          <t>is_supply</t>
         </is>
       </c>
       <c r="H98" t="b">
@@ -33384,7 +33384,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>LCC_financial</t>
+          <t>lcc_financial</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -33470,7 +33470,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -33561,7 +33561,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -33652,7 +33652,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -33743,7 +33743,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Service provided</t>
+          <t>service_provide</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -33775,7 +33775,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Competition type</t>
+          <t>competition</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -33807,7 +33807,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Is supply</t>
+          <t>is_supply</t>
         </is>
       </c>
       <c r="H105" t="b">
@@ -33837,7 +33837,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>LCC_financial</t>
+          <t>lcc_financial</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -33923,7 +33923,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -34014,7 +34014,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -34105,7 +34105,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -34196,7 +34196,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Service provided</t>
+          <t>service_provide</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -34228,7 +34228,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Competition type</t>
+          <t>competition</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -34260,7 +34260,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Is supply</t>
+          <t>is_supply</t>
         </is>
       </c>
       <c r="H112" t="b">
@@ -34290,7 +34290,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>LCC_financial</t>
+          <t>lcc_financial</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -34365,7 +34365,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Emissions_biomass</t>
+          <t>emissions_biomass</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -34456,7 +34456,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -34536,7 +34536,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -34627,7 +34627,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -34718,7 +34718,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Service provided</t>
+          <t>service_provide</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -34750,7 +34750,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Competition type</t>
+          <t>competition</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -34782,7 +34782,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Is supply</t>
+          <t>is_supply</t>
         </is>
       </c>
       <c r="H120" t="b">
@@ -34812,7 +34812,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>LCC_financial</t>
+          <t>lcc_financial</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -34887,7 +34887,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Emissions_biomass</t>
+          <t>emissions_biomass</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -34978,7 +34978,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -35058,7 +35058,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -35149,7 +35149,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -35240,7 +35240,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Service provided</t>
+          <t>service_provide</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -35272,7 +35272,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Competition type</t>
+          <t>competition</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -35304,7 +35304,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Is supply</t>
+          <t>is_supply</t>
         </is>
       </c>
       <c r="H128" t="b">
@@ -35334,7 +35334,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>LCC_financial</t>
+          <t>lcc_financial</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -35420,7 +35420,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Emissions_biomass</t>
+          <t>emissions_biomass</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -35511,7 +35511,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -35602,7 +35602,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -35693,7 +35693,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -35784,7 +35784,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Service provided</t>
+          <t>service_provide</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -35816,7 +35816,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Competition type</t>
+          <t>competition</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -35848,7 +35848,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Is supply</t>
+          <t>is_supply</t>
         </is>
       </c>
       <c r="H136" t="b">
@@ -35878,7 +35878,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>LCC_financial</t>
+          <t>lcc_financial</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -35964,7 +35964,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -36055,7 +36055,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -36146,7 +36146,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -36237,7 +36237,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Service provided</t>
+          <t>service_provide</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -36269,7 +36269,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Competition type</t>
+          <t>competition</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -36301,7 +36301,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Is supply</t>
+          <t>is_supply</t>
         </is>
       </c>
       <c r="H143" t="b">
@@ -36331,7 +36331,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>LCC_financial</t>
+          <t>lcc_financial</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -36417,7 +36417,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -36508,7 +36508,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -36599,7 +36599,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -36690,7 +36690,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Service provided</t>
+          <t>service_provide</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -36722,7 +36722,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Competition type</t>
+          <t>competition</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -36754,7 +36754,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>LCC_financial</t>
+          <t>lcc_financial</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
